--- a/artfynd/A 37925-2026 artfynd.xlsx
+++ b/artfynd/A 37925-2026 artfynd.xlsx
@@ -1107,7 +1107,7 @@
         <v>136532088</v>
       </c>
       <c r="B6" t="n">
-        <v>99259</v>
+        <v>99262</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136532707</v>
       </c>
       <c r="B7" t="n">
-        <v>99259</v>
+        <v>99262</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136533976</v>
       </c>
       <c r="B8" t="n">
-        <v>99344</v>
+        <v>99347</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>136532248</v>
       </c>
       <c r="B9" t="n">
-        <v>108105</v>
+        <v>108108</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>136531846</v>
       </c>
       <c r="B10" t="n">
-        <v>110313</v>
+        <v>110316</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>136530721</v>
       </c>
       <c r="B11" t="n">
-        <v>98271</v>
+        <v>98274</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 37925-2026 artfynd.xlsx
+++ b/artfynd/A 37925-2026 artfynd.xlsx
@@ -1107,7 +1107,7 @@
         <v>136532088</v>
       </c>
       <c r="B6" t="n">
-        <v>99262</v>
+        <v>99263</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136532707</v>
       </c>
       <c r="B7" t="n">
-        <v>99262</v>
+        <v>99263</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136533976</v>
       </c>
       <c r="B8" t="n">
-        <v>99347</v>
+        <v>99348</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>136532248</v>
       </c>
       <c r="B9" t="n">
-        <v>108108</v>
+        <v>108109</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>136531846</v>
       </c>
       <c r="B10" t="n">
-        <v>110316</v>
+        <v>110317</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>136530721</v>
       </c>
       <c r="B11" t="n">
-        <v>98274</v>
+        <v>98275</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 37925-2026 artfynd.xlsx
+++ b/artfynd/A 37925-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136530939</v>
       </c>
       <c r="B2" t="n">
-        <v>43280</v>
+        <v>43282</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136532222</v>
       </c>
       <c r="B3" t="n">
-        <v>43280</v>
+        <v>43282</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136532708</v>
       </c>
       <c r="B4" t="n">
-        <v>43280</v>
+        <v>43282</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136532798</v>
       </c>
       <c r="B5" t="n">
-        <v>43280</v>
+        <v>43282</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136532088</v>
       </c>
       <c r="B6" t="n">
-        <v>99263</v>
+        <v>99268</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136532707</v>
       </c>
       <c r="B7" t="n">
-        <v>99263</v>
+        <v>99268</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136533976</v>
       </c>
       <c r="B8" t="n">
-        <v>99348</v>
+        <v>99353</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>136532248</v>
       </c>
       <c r="B9" t="n">
-        <v>108109</v>
+        <v>108114</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>136531846</v>
       </c>
       <c r="B10" t="n">
-        <v>110317</v>
+        <v>110322</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>136530721</v>
       </c>
       <c r="B11" t="n">
-        <v>98275</v>
+        <v>98280</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 37925-2026 artfynd.xlsx
+++ b/artfynd/A 37925-2026 artfynd.xlsx
@@ -1107,7 +1107,7 @@
         <v>136532088</v>
       </c>
       <c r="B6" t="n">
-        <v>99268</v>
+        <v>99270</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136532707</v>
       </c>
       <c r="B7" t="n">
-        <v>99268</v>
+        <v>99270</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136533976</v>
       </c>
       <c r="B8" t="n">
-        <v>99353</v>
+        <v>99355</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>136532248</v>
       </c>
       <c r="B9" t="n">
-        <v>108114</v>
+        <v>108116</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>136531846</v>
       </c>
       <c r="B10" t="n">
-        <v>110322</v>
+        <v>110324</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>136530721</v>
       </c>
       <c r="B11" t="n">
-        <v>98280</v>
+        <v>98282</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 37925-2026 artfynd.xlsx
+++ b/artfynd/A 37925-2026 artfynd.xlsx
@@ -1107,7 +1107,7 @@
         <v>136532088</v>
       </c>
       <c r="B6" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136532707</v>
       </c>
       <c r="B7" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136533976</v>
       </c>
       <c r="B8" t="n">
-        <v>99355</v>
+        <v>99361</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Björn Almkvist</t>
+          <t>Björn Almkvist, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1425,7 +1425,7 @@
         <v>136532248</v>
       </c>
       <c r="B9" t="n">
-        <v>108116</v>
+        <v>108122</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>136531846</v>
       </c>
       <c r="B10" t="n">
-        <v>110324</v>
+        <v>110330</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>136530721</v>
       </c>
       <c r="B11" t="n">
-        <v>98282</v>
+        <v>98288</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 37925-2026 artfynd.xlsx
+++ b/artfynd/A 37925-2026 artfynd.xlsx
@@ -1107,7 +1107,7 @@
         <v>136532088</v>
       </c>
       <c r="B6" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136532707</v>
       </c>
       <c r="B7" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136533976</v>
       </c>
       <c r="B8" t="n">
-        <v>99361</v>
+        <v>99363</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Björn Almkvist, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Björn Almkvist</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1425,7 +1425,7 @@
         <v>136532248</v>
       </c>
       <c r="B9" t="n">
-        <v>108122</v>
+        <v>108124</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>136531846</v>
       </c>
       <c r="B10" t="n">
-        <v>110330</v>
+        <v>110332</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>136530721</v>
       </c>
       <c r="B11" t="n">
-        <v>98288</v>
+        <v>98290</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 37925-2026 artfynd.xlsx
+++ b/artfynd/A 37925-2026 artfynd.xlsx
@@ -1107,7 +1107,7 @@
         <v>136532088</v>
       </c>
       <c r="B6" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136532707</v>
       </c>
       <c r="B7" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136533976</v>
       </c>
       <c r="B8" t="n">
-        <v>99363</v>
+        <v>99364</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>136532248</v>
       </c>
       <c r="B9" t="n">
-        <v>108124</v>
+        <v>108125</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>136531846</v>
       </c>
       <c r="B10" t="n">
-        <v>110332</v>
+        <v>110333</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>136530721</v>
       </c>
       <c r="B11" t="n">
-        <v>98290</v>
+        <v>98291</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 37925-2026 artfynd.xlsx
+++ b/artfynd/A 37925-2026 artfynd.xlsx
@@ -1107,7 +1107,7 @@
         <v>136532088</v>
       </c>
       <c r="B6" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136532707</v>
       </c>
       <c r="B7" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136533976</v>
       </c>
       <c r="B8" t="n">
-        <v>99364</v>
+        <v>99370</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>136532248</v>
       </c>
       <c r="B9" t="n">
-        <v>108125</v>
+        <v>108131</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>136531846</v>
       </c>
       <c r="B10" t="n">
-        <v>110333</v>
+        <v>110339</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>136530721</v>
       </c>
       <c r="B11" t="n">
-        <v>98291</v>
+        <v>98297</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 37925-2026 artfynd.xlsx
+++ b/artfynd/A 37925-2026 artfynd.xlsx
@@ -1107,7 +1107,7 @@
         <v>136532088</v>
       </c>
       <c r="B6" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136532707</v>
       </c>
       <c r="B7" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136533976</v>
       </c>
       <c r="B8" t="n">
-        <v>99370</v>
+        <v>99374</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>136532248</v>
       </c>
       <c r="B9" t="n">
-        <v>108131</v>
+        <v>108135</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>136531846</v>
       </c>
       <c r="B10" t="n">
-        <v>110339</v>
+        <v>110343</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>136530721</v>
       </c>
       <c r="B11" t="n">
-        <v>98297</v>
+        <v>98301</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 37925-2026 artfynd.xlsx
+++ b/artfynd/A 37925-2026 artfynd.xlsx
@@ -1107,7 +1107,7 @@
         <v>136532088</v>
       </c>
       <c r="B6" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136532707</v>
       </c>
       <c r="B7" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136533976</v>
       </c>
       <c r="B8" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>136532248</v>
       </c>
       <c r="B9" t="n">
-        <v>108135</v>
+        <v>108137</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>136531846</v>
       </c>
       <c r="B10" t="n">
-        <v>110343</v>
+        <v>110345</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>136530721</v>
       </c>
       <c r="B11" t="n">
-        <v>98301</v>
+        <v>98303</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 37925-2026 artfynd.xlsx
+++ b/artfynd/A 37925-2026 artfynd.xlsx
@@ -1107,7 +1107,7 @@
         <v>136532088</v>
       </c>
       <c r="B6" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136532707</v>
       </c>
       <c r="B7" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136533976</v>
       </c>
       <c r="B8" t="n">
-        <v>99376</v>
+        <v>99378</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>136532248</v>
       </c>
       <c r="B9" t="n">
-        <v>108137</v>
+        <v>108139</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>136531846</v>
       </c>
       <c r="B10" t="n">
-        <v>110345</v>
+        <v>110347</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>136530721</v>
       </c>
       <c r="B11" t="n">
-        <v>98303</v>
+        <v>98305</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 37925-2026 artfynd.xlsx
+++ b/artfynd/A 37925-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136530939</v>
       </c>
       <c r="B2" t="n">
-        <v>43282</v>
+        <v>43295</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136532222</v>
       </c>
       <c r="B3" t="n">
-        <v>43282</v>
+        <v>43295</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136532708</v>
       </c>
       <c r="B4" t="n">
-        <v>43282</v>
+        <v>43295</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136532798</v>
       </c>
       <c r="B5" t="n">
-        <v>43282</v>
+        <v>43295</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136532088</v>
       </c>
       <c r="B6" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136532707</v>
       </c>
       <c r="B7" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136533976</v>
       </c>
       <c r="B8" t="n">
-        <v>99378</v>
+        <v>99391</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>136532248</v>
       </c>
       <c r="B9" t="n">
-        <v>108139</v>
+        <v>108152</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>136531846</v>
       </c>
       <c r="B10" t="n">
-        <v>110347</v>
+        <v>110360</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>136530721</v>
       </c>
       <c r="B11" t="n">
-        <v>98305</v>
+        <v>98318</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 37925-2026 artfynd.xlsx
+++ b/artfynd/A 37925-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136530939</v>
       </c>
       <c r="B2" t="n">
-        <v>43295</v>
+        <v>43297</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136532222</v>
       </c>
       <c r="B3" t="n">
-        <v>43295</v>
+        <v>43297</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136532708</v>
       </c>
       <c r="B4" t="n">
-        <v>43295</v>
+        <v>43297</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136532798</v>
       </c>
       <c r="B5" t="n">
-        <v>43295</v>
+        <v>43297</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136532088</v>
       </c>
       <c r="B6" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136532707</v>
       </c>
       <c r="B7" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136533976</v>
       </c>
       <c r="B8" t="n">
-        <v>99391</v>
+        <v>99393</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>136532248</v>
       </c>
       <c r="B9" t="n">
-        <v>108152</v>
+        <v>108154</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>136531846</v>
       </c>
       <c r="B10" t="n">
-        <v>110360</v>
+        <v>110362</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>136530721</v>
       </c>
       <c r="B11" t="n">
-        <v>98318</v>
+        <v>98320</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
